--- a/data/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/model_ledgers/npb-tie-aware-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -974,8 +974,212 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>9964062e0c54497a</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>347e825468ed22f4a2d199c77ecdf45f63f172267afce60f945654c0e7e89f1f</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67498</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.550397</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.011226493087557632</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:21:34.543522Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>d3638d88917b4333</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>fe60ea981cb60cbb4cd1f8007017436a9fb4fad2d99764931f7f0d7461cd4907</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>67498</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.550397</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.0008474504504505376</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:33:34.636987Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ4"/>
+  <autoFilter ref="A1:AJ6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/model_ledgers/npb-tie-aware-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1178,8 +1178,1232 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6129b8d71546470a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77187</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.50388</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>-0.015350769230769168</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:47.587244Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12d4c88cd5a042f3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77188</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.50975</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>-0.03979954954954945</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:48.155003Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ba3057c039d0467c</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>77189</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.514457</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>-0.004773769230769109</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:48.710584Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>16cc295d26fd4178</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77190</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.548012</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>-0.051988000000000034</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:49.285357Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>f1b3cda489f648b3</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77186</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.507038</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>-0.023478431924882637</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:49.814385Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>de88669f50d24307</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>477f1c5c7e60f1b4dad07c7d2b98e23450e2dfd5a709583611163bd42dc9691f</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>77191</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.666743</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.006879054421768616</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:50.327867Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1bc9ceb9fe6b471f</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77187</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.50388</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.015350769230769168</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:34.900584Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>abf6f0e5ef7049fd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77188</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.50975</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>-0.03979954954954945</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.510747Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>947df36c28ea4057</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>77189</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.514457</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.004773769230769109</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.017681Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>dea5973d89c041ba</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>77190</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.548012</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>-0.061362999999999945</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.479497Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>d803876549fc4da3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77186</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.507038</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>-0.0425115495495495</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.966712Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>083e06106b434bb2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>77191</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.666743</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.0032239966996699954</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449581Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AJ18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>